--- a/Excel/EquipReformConfig.xlsx
+++ b/Excel/EquipReformConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="24">
   <si>
     <t>_id</t>
   </si>
@@ -41,6 +41,9 @@
     <t>AttrValueList</t>
   </si>
   <si>
+    <t>RequireLevel</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -56,19 +59,22 @@
     <t>1</t>
   </si>
   <si>
-    <t>2001,2003</t>
-  </si>
-  <si>
-    <t>1,2</t>
+    <t>2001,2003,2010</t>
+  </si>
+  <si>
+    <t>1,2,1</t>
+  </si>
+  <si>
+    <t>0,0,500</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>2002,2003</t>
-  </si>
-  <si>
-    <t>3,2</t>
+    <t>2002,2003,2001</t>
+  </si>
+  <si>
+    <t>3,2,1</t>
   </si>
   <si>
     <t>3</t>
@@ -725,12 +731,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1060,254 +1065,318 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFB15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="4" width="8.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="26" style="3" customWidth="1"/>
-    <col min="6" max="6" width="22.25" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.5" style="1" customWidth="1"/>
-    <col min="8" max="16380" width="9" style="1"/>
-    <col min="16381" max="16382" width="9" style="2"/>
-    <col min="16383" max="16384" width="9" style="4"/>
+    <col min="6" max="8" width="22.25" style="3" customWidth="1"/>
+    <col min="9" max="16380" width="9" style="1"/>
+    <col min="16381" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="5:6">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="5:8">
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="3:6">
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="3:6">
-      <c r="C3" s="6" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="3:6">
-      <c r="C4" s="6" t="s">
+      <c r="G3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="6" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="3:6">
-      <c r="C5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="D5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+      <c r="F5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:8">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
-      <c r="C6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="XFA6" s="4"/>
-      <c r="XFB6" s="4"/>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+      <c r="F6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:8">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="8" t="s">
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="XFA7" s="4"/>
-      <c r="XFB7" s="4"/>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:8">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="C8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="8" t="s">
+      <c r="C8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="XFA8" s="4"/>
-      <c r="XFB8" s="4"/>
-    </row>
-    <row r="9" s="2" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+      <c r="F8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:8">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="G9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="XFA9" s="4"/>
-      <c r="XFB9" s="4"/>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:8">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
-      <c r="C10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="8" t="s">
+      <c r="C10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="XFA10" s="4"/>
-      <c r="XFB10" s="4"/>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:8">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="8" t="s">
+      <c r="C11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="XFA11" s="4"/>
-      <c r="XFB11" s="4"/>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:8">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="8" t="s">
+      <c r="C12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="XFA12" s="4"/>
-      <c r="XFB12" s="4"/>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+      <c r="F12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:8">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
-      <c r="C13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="8" t="s">
+      <c r="C13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="XFA13" s="4"/>
-      <c r="XFB13" s="4"/>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+      <c r="F13" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:8">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="8" t="s">
+      <c r="C14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="XFA14" s="4"/>
-      <c r="XFB14" s="4"/>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="24" customHeight="1" spans="1:16382">
+      <c r="F14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:8">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="C15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="XFA15" s="4"/>
-      <c r="XFB15" s="4"/>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:2">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:D2 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipReformConfig.xlsx
+++ b/Excel/EquipReformConfig.xlsx
@@ -59,22 +59,22 @@
     <t>1</t>
   </si>
   <si>
-    <t>2001,2003,2010</t>
-  </si>
-  <si>
-    <t>1,2,1</t>
-  </si>
-  <si>
-    <t>0,0,500</t>
+    <t>2001,2003,2010,2013</t>
+  </si>
+  <si>
+    <t>1,2,1,2</t>
+  </si>
+  <si>
+    <t>0,0,500,800</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>2002,2003,2001</t>
-  </si>
-  <si>
-    <t>3,2,1</t>
+    <t>2002,2003,2001,2013</t>
+  </si>
+  <si>
+    <t>3,2,1,2</t>
   </si>
   <si>
     <t>3</t>
@@ -1076,13 +1076,13 @@
     <col min="16381" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="5:8">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="3"/>
@@ -1090,7 +1090,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="C4" s="5" t="s">
         <v>5</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="C5" s="5" t="s">
         <v>6</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:2">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:8">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
     </row>
